--- a/ig/DM-JANVIER-2025/ValueSet-1.2.250.1.213.1.1.5.42.xlsx
+++ b/ig/DM-JANVIER-2025/ValueSet-1.2.250.1.213.1.1.5.42.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241018000000</t>
+    <t>20241230000000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T00:00:00+01:00</t>
+    <t>2024-12-30T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -150,34 +150,34 @@
     <t>Psychologue</t>
   </si>
   <si>
-    <t>97</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R95-UsagerTitre/FHIR/TRE-R95-UsagerTitre</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Assistant de service social</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R94-ProfessionSocial/FHIR/TRE-R94-ProfessionSocial</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Autre professionnel</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>Educateur spécialisé</t>
+  </si>
+  <si>
+    <t>329</t>
   </si>
   <si>
     <t>Conseiller en génétique</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R95-UsagerTitre/FHIR/TRE-R95-UsagerTitre</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Assistant de service social</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>Educateur spécialisé</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R94-ProfessionSocial/FHIR/TRE-R94-ProfessionSocial</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Autre professionnel</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -555,26 +555,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -583,60 +575,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -655,10 +593,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -674,6 +612,68 @@
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>54</v>
       </c>
     </row>
